--- a/tame_output/ON/bt/strategyON_20231025.xlsx
+++ b/tame_output/ON/bt/strategyON_20231025.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -1054,26 +1054,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>101.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-157.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.9%</t>
+          <t>131.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1760"/>
+  <dimension ref="A1:G1761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41990,7 +41990,7 @@
         <v>45222</v>
       </c>
       <c r="B1760" t="n">
-        <v>3.066950654063524</v>
+        <v>3.048806209055149</v>
       </c>
       <c r="C1760" t="n">
         <v>2.992474709334104</v>
@@ -42006,6 +42006,29 @@
       </c>
       <c r="G1760" t="n">
         <v>4.286856274436318</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="2" t="n">
+        <v>45223</v>
+      </c>
+      <c r="B1761" t="n">
+        <v>3.045961362411172</v>
+      </c>
+      <c r="C1761" t="n">
+        <v>3.010249418375564</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>1.525715015952012</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>3.620179000442622</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>2.157409806615064</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>4.304695302344604</v>
       </c>
     </row>
   </sheetData>
